--- a/Bike_Sales_Outlier_Lab.xlsx
+++ b/Bike_Sales_Outlier_Lab.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dropbox\Dropbox\Cisco Aries\2022\Data Pathway Course Development\Course 1\Rework\csv files for reworked labs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00FEFAE0-DE00-419C-BA87-533F9603AF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01D0575-94E9-4BB2-8F43-A174AB047243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Bike Sales" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="3" r:id="rId1"/>
+    <sheet name="Bike Sales" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bike Sales'!$A$1:$S$89</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
+  <pivotCaches>
+    <pivotCache cacheId="11" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,8 +39,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="162">
   <si>
     <t>Sales_Order #</t>
   </si>
@@ -501,6 +530,24 @@
   </si>
   <si>
     <t>000261782</t>
+  </si>
+  <si>
+    <t>Etiquetas de fila</t>
+  </si>
+  <si>
+    <t>Total general</t>
+  </si>
+  <si>
+    <t>Suma de Order_Quantity</t>
+  </si>
+  <si>
+    <t>Valor más alto</t>
+  </si>
+  <si>
+    <t>5 valores más altos</t>
+  </si>
+  <si>
+    <t>6 valores más bajos</t>
   </si>
 </sst>
 </file>
@@ -508,9 +555,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -664,8 +711,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -845,8 +900,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -961,6 +1022,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1006,10 +1076,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1022,50 +1092,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Bueno" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Celda de comprobación" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Celda vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Encabezado 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Encabezado 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Énfasis1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Énfasis2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Énfasis3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Énfasis4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Énfasis5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Énfasis6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Incorrecto" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Notas" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Salida" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texto de advertencia" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Texto explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Título" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Título 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1080,10 +1160,4248 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja2!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Suma de Order_Quantity</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja2!$E$2:$E$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-76CE-400E-BA7B-FEF9F4A285A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2092952912"/>
+        <c:axId val="1639043568"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2092952912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1639043568"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1639043568"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2092952912"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CO"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja2!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Suma de Order_Quantity</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja2!$D$2:$D$25</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>44531</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44532</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44533</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44534</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>44535</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>44536</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>44537</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44538</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>44539</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>44540</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>44541</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>44542</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>44543</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>44544</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>44545</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>44546</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>44547</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44548</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>44549</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>44550</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>44551</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>44552</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>44553</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>44554</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja2!$E$2:$E$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BA6A-47A5-B315-BAE4A965BF0C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="270522048"/>
+        <c:axId val="50685008"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="270522048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50685008"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="50685008"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="270522048"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CO"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>434748</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>18142</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>244928</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD907A1F-19E8-6309-2DF7-FDA04BB01BBD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>439964</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>2722</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>263071</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24319895-7182-D1D1-C02B-662632FD0190}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="User" refreshedDate="46284.947482754629" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="88" xr:uid="{46F1B598-5527-45BF-8EE6-4E0595A6B137}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:S89" sheet="Bike Sales"/>
+  </cacheSource>
+  <cacheFields count="19">
+    <cacheField name="Sales_Order #" numFmtId="49">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2021-12-01T00:00:00" maxDate="2021-12-25T00:00:00" count="24">
+        <d v="2021-12-01T00:00:00"/>
+        <d v="2021-12-02T00:00:00"/>
+        <d v="2021-12-03T00:00:00"/>
+        <d v="2021-12-04T00:00:00"/>
+        <d v="2021-12-05T00:00:00"/>
+        <d v="2021-12-06T00:00:00"/>
+        <d v="2021-12-07T00:00:00"/>
+        <d v="2021-12-08T00:00:00"/>
+        <d v="2021-12-09T00:00:00"/>
+        <d v="2021-12-10T00:00:00"/>
+        <d v="2021-12-11T00:00:00"/>
+        <d v="2021-12-12T00:00:00"/>
+        <d v="2021-12-13T00:00:00"/>
+        <d v="2021-12-14T00:00:00"/>
+        <d v="2021-12-15T00:00:00"/>
+        <d v="2021-12-16T00:00:00"/>
+        <d v="2021-12-17T00:00:00"/>
+        <d v="2021-12-18T00:00:00"/>
+        <d v="2021-12-19T00:00:00"/>
+        <d v="2021-12-20T00:00:00"/>
+        <d v="2021-12-21T00:00:00"/>
+        <d v="2021-12-22T00:00:00"/>
+        <d v="2021-12-23T00:00:00"/>
+        <d v="2021-12-24T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Day" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="24"/>
+    </cacheField>
+    <cacheField name="Month" numFmtId="0">
+      <sharedItems count="1">
+        <s v="December"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Year" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2021" maxValue="2021"/>
+    </cacheField>
+    <cacheField name="Customer_Age" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="17" maxValue="63"/>
+    </cacheField>
+    <cacheField name="Age_Group" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Adults (35-64)"/>
+        <s v="Young Adults (25-34)"/>
+        <s v="Youth (&lt;25)"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Customer_Gender" numFmtId="0">
+      <sharedItems count="2">
+        <s v="F"/>
+        <s v="M"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Country" numFmtId="0">
+      <sharedItems count="6">
+        <s v="United States"/>
+        <s v="United Kingdom"/>
+        <s v="Australia"/>
+        <s v="Germany"/>
+        <s v="Canada"/>
+        <s v="France"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="State" numFmtId="0">
+      <sharedItems count="17">
+        <s v="California"/>
+        <s v="England"/>
+        <s v="New South Wales"/>
+        <s v="Washington"/>
+        <s v="Nordrhein-Westfalen"/>
+        <s v="Queensland"/>
+        <s v="British Columbia"/>
+        <s v="Oregon"/>
+        <s v="Victoria"/>
+        <s v="Hamburg"/>
+        <s v="Seine (Paris)"/>
+        <s v="Seine et Marne"/>
+        <s v="Seine Saint Denis"/>
+        <s v="Nord"/>
+        <s v="South Australia"/>
+        <s v="Hessen"/>
+        <s v="Somme"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Product_Category" numFmtId="0">
+      <sharedItems count="1">
+        <s v="Bikes"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Sub_Category" numFmtId="0">
+      <sharedItems count="1">
+        <s v="Mountain Bikes"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Product_Description" numFmtId="0">
+      <sharedItems count="18">
+        <s v="Mountain-200 Black, 46"/>
+        <s v="Mountain-200 Silver, 42"/>
+        <s v="Mountain-400-W Silver, 46"/>
+        <s v="Mountain-400-W Silver, 42"/>
+        <s v="Mountain-200 Black, 38"/>
+        <s v="Mountain-200 Silver, 38"/>
+        <s v="Mountain-200 Black, 42"/>
+        <s v="Mountain-400-W Silver, 38"/>
+        <s v="Mountain-500 Silver, 42"/>
+        <s v="Mountain-500 Black, 42"/>
+        <s v="Mountain-100 Black, 38"/>
+        <s v="Mountain-500 Black, 40"/>
+        <s v="Mountain-100 Silver, 44"/>
+        <s v="Mountain-500 Silver, 40"/>
+        <s v="Mountain-200 Silver, 46"/>
+        <s v="Mountain-500 Black, 44"/>
+        <s v="Mountain-100 Black, 48"/>
+        <s v="Mountain-500 Black, 52"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Order_Quantity" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="11"/>
+    </cacheField>
+    <cacheField name=" Unit_Cost " numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="295" maxValue="1912"/>
+    </cacheField>
+    <cacheField name=" Unit_Price " numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="540" maxValue="3400"/>
+    </cacheField>
+    <cacheField name=" Profit " numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="245" maxValue="5908"/>
+    </cacheField>
+    <cacheField name=" Cost " numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="295" maxValue="13926"/>
+    </cacheField>
+    <cacheField name="Revenue" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="540" maxValue="25520"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="88">
+  <r>
+    <s v="000261696"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="39"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="4172"/>
+    <n v="5008"/>
+    <n v="9180"/>
+  </r>
+  <r>
+    <s v="000261695"/>
+    <x v="0"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="44"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261697"/>
+    <x v="1"/>
+    <n v="2"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="37"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="2"/>
+    <n v="420"/>
+    <n v="769"/>
+    <n v="698"/>
+    <n v="840"/>
+    <n v="1538"/>
+  </r>
+  <r>
+    <s v="000261698"/>
+    <x v="1"/>
+    <n v="2"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="31"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="1"/>
+    <n v="420"/>
+    <n v="769"/>
+    <n v="349"/>
+    <n v="420"/>
+    <n v="769"/>
+  </r>
+  <r>
+    <s v="000261699"/>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="37"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="2086"/>
+    <n v="2504"/>
+    <n v="4590"/>
+  </r>
+  <r>
+    <s v="000261700"/>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="24"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261701"/>
+    <x v="2"/>
+    <n v="3"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="37"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261702"/>
+    <x v="3"/>
+    <n v="4"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="31"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="4"/>
+    <n v="420"/>
+    <n v="769"/>
+    <n v="1396"/>
+    <n v="1680"/>
+    <n v="3076"/>
+  </r>
+  <r>
+    <s v="000261703"/>
+    <x v="4"/>
+    <n v="5"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="39"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="4172"/>
+    <n v="5008"/>
+    <n v="9180"/>
+  </r>
+  <r>
+    <s v="000261704"/>
+    <x v="4"/>
+    <n v="5"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="42"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="4"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="4172"/>
+    <n v="5008"/>
+    <n v="9180"/>
+  </r>
+  <r>
+    <s v="000261705"/>
+    <x v="4"/>
+    <n v="5"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="35"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261706"/>
+    <x v="4"/>
+    <n v="5"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="37"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261707"/>
+    <x v="5"/>
+    <n v="6"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="23"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="420"/>
+    <n v="769"/>
+    <n v="1047"/>
+    <n v="1260"/>
+    <n v="2307"/>
+  </r>
+  <r>
+    <s v="000261708"/>
+    <x v="5"/>
+    <n v="6"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="27"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261709"/>
+    <x v="5"/>
+    <n v="6"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="36"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261710"/>
+    <x v="5"/>
+    <n v="6"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="47"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261711"/>
+    <x v="6"/>
+    <n v="7"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="30"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="7"/>
+    <n v="4"/>
+    <n v="420"/>
+    <n v="769"/>
+    <n v="1396"/>
+    <n v="1680"/>
+    <n v="3076"/>
+  </r>
+  <r>
+    <s v="000261712"/>
+    <x v="6"/>
+    <n v="7"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="38"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="2108"/>
+    <n v="2532"/>
+    <n v="4640"/>
+  </r>
+  <r>
+    <s v="000261713"/>
+    <x v="7"/>
+    <n v="8"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="19"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="8"/>
+    <n v="4"/>
+    <n v="308"/>
+    <n v="565"/>
+    <n v="1028"/>
+    <n v="1232"/>
+    <n v="2260"/>
+  </r>
+  <r>
+    <s v="000261714"/>
+    <x v="7"/>
+    <n v="8"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="30"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="4"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="4216"/>
+    <n v="5064"/>
+    <n v="9280"/>
+  </r>
+  <r>
+    <s v="000261715"/>
+    <x v="7"/>
+    <n v="8"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="39"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="9"/>
+    <n v="2"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="2086"/>
+    <n v="2504"/>
+    <n v="4590"/>
+  </r>
+  <r>
+    <s v="000261716"/>
+    <x v="7"/>
+    <n v="8"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="35"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="9"/>
+    <n v="1"/>
+    <n v="295"/>
+    <n v="540"/>
+    <n v="245"/>
+    <n v="295"/>
+    <n v="540"/>
+  </r>
+  <r>
+    <s v="000261717"/>
+    <x v="8"/>
+    <n v="9"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="33"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="10"/>
+    <n v="2"/>
+    <n v="1898"/>
+    <n v="3375"/>
+    <n v="2954"/>
+    <n v="3796"/>
+    <n v="6750"/>
+  </r>
+  <r>
+    <s v="000261718"/>
+    <x v="8"/>
+    <n v="9"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="41"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261719"/>
+    <x v="9"/>
+    <n v="10"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="34"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="2"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="2086"/>
+    <n v="2504"/>
+    <n v="4590"/>
+  </r>
+  <r>
+    <s v="000261720"/>
+    <x v="9"/>
+    <n v="10"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="40"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="2"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="2086"/>
+    <n v="2504"/>
+    <n v="4590"/>
+  </r>
+  <r>
+    <s v="000261721"/>
+    <x v="9"/>
+    <n v="10"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="26"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261722"/>
+    <x v="9"/>
+    <n v="10"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="34"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="11"/>
+    <n v="1"/>
+    <n v="295"/>
+    <n v="540"/>
+    <n v="245"/>
+    <n v="295"/>
+    <n v="540"/>
+  </r>
+  <r>
+    <s v="000261723"/>
+    <x v="9"/>
+    <n v="10"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="34"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="12"/>
+    <n v="1"/>
+    <n v="1912"/>
+    <n v="3400"/>
+    <n v="1488"/>
+    <n v="1912"/>
+    <n v="3400"/>
+  </r>
+  <r>
+    <s v="000261724"/>
+    <x v="9"/>
+    <n v="10"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="38"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261725"/>
+    <x v="10"/>
+    <n v="11"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="24"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="3"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="3129"/>
+    <n v="3756"/>
+    <n v="6885"/>
+  </r>
+  <r>
+    <s v="000261726"/>
+    <x v="10"/>
+    <n v="11"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="41"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="7"/>
+    <n v="2"/>
+    <n v="420"/>
+    <n v="769"/>
+    <n v="698"/>
+    <n v="840"/>
+    <n v="1538"/>
+  </r>
+  <r>
+    <s v="000261727"/>
+    <x v="10"/>
+    <n v="11"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="27"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261728"/>
+    <x v="10"/>
+    <n v="11"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="37"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1"/>
+    <n v="420"/>
+    <n v="769"/>
+    <n v="349"/>
+    <n v="420"/>
+    <n v="769"/>
+  </r>
+  <r>
+    <s v="000261729"/>
+    <x v="10"/>
+    <n v="11"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="38"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261730"/>
+    <x v="11"/>
+    <n v="12"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="36"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="4216"/>
+    <n v="5064"/>
+    <n v="9280"/>
+  </r>
+  <r>
+    <s v="000261731"/>
+    <x v="11"/>
+    <n v="12"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="37"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="4"/>
+    <n v="420"/>
+    <n v="769"/>
+    <n v="1396"/>
+    <n v="1680"/>
+    <n v="3076"/>
+  </r>
+  <r>
+    <s v="000261732"/>
+    <x v="11"/>
+    <n v="12"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="34"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="2"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="2086"/>
+    <n v="2504"/>
+    <n v="4590"/>
+  </r>
+  <r>
+    <s v="000261733"/>
+    <x v="11"/>
+    <n v="12"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="35"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261734"/>
+    <x v="11"/>
+    <n v="12"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="38"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261735"/>
+    <x v="12"/>
+    <n v="13"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="32"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="3162"/>
+    <n v="3798"/>
+    <n v="6960"/>
+  </r>
+  <r>
+    <s v="000261736"/>
+    <x v="12"/>
+    <n v="13"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="40"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="13"/>
+    <n v="1"/>
+    <n v="308"/>
+    <n v="565"/>
+    <n v="257"/>
+    <n v="308"/>
+    <n v="565"/>
+  </r>
+  <r>
+    <s v="000261737"/>
+    <x v="12"/>
+    <n v="13"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="44"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261738"/>
+    <x v="12"/>
+    <n v="13"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="49"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261739"/>
+    <x v="13"/>
+    <n v="14"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="30"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="2"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="2108"/>
+    <n v="2532"/>
+    <n v="4640"/>
+  </r>
+  <r>
+    <s v="000261740"/>
+    <x v="13"/>
+    <n v="14"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="32"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261741"/>
+    <x v="13"/>
+    <n v="14"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="32"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1"/>
+    <n v="420"/>
+    <n v="769"/>
+    <n v="349"/>
+    <n v="420"/>
+    <n v="769"/>
+  </r>
+  <r>
+    <s v="000261742"/>
+    <x v="14"/>
+    <n v="15"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="29"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261743"/>
+    <x v="15"/>
+    <n v="16"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="33"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="2"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="2086"/>
+    <n v="2504"/>
+    <n v="4590"/>
+  </r>
+  <r>
+    <s v="000261744"/>
+    <x v="15"/>
+    <n v="16"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="38"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="2"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="2086"/>
+    <n v="2504"/>
+    <n v="4590"/>
+  </r>
+  <r>
+    <s v="000261745"/>
+    <x v="15"/>
+    <n v="16"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="27"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="11"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="14"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261746"/>
+    <x v="16"/>
+    <n v="17"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="37"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="2"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="2108"/>
+    <n v="2532"/>
+    <n v="4640"/>
+  </r>
+  <r>
+    <s v="000261747"/>
+    <x v="16"/>
+    <n v="17"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="31"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="1"/>
+    <n v="420"/>
+    <n v="769"/>
+    <n v="349"/>
+    <n v="420"/>
+    <n v="769"/>
+  </r>
+  <r>
+    <s v="000261748"/>
+    <x v="16"/>
+    <n v="17"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="42"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="14"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261749"/>
+    <x v="17"/>
+    <n v="18"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="35"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="8"/>
+    <n v="4"/>
+    <n v="308"/>
+    <n v="565"/>
+    <n v="1028"/>
+    <n v="1232"/>
+    <n v="2260"/>
+  </r>
+  <r>
+    <s v="000261750"/>
+    <x v="17"/>
+    <n v="18"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="38"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="14"/>
+    <n v="4"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="4216"/>
+    <n v="5064"/>
+    <n v="9280"/>
+  </r>
+  <r>
+    <s v="000261751"/>
+    <x v="17"/>
+    <n v="18"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="24"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="12"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="3"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="3162"/>
+    <n v="3798"/>
+    <n v="6960"/>
+  </r>
+  <r>
+    <s v="000261752"/>
+    <x v="17"/>
+    <n v="18"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="26"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="3"/>
+    <n v="420"/>
+    <n v="769"/>
+    <n v="1047"/>
+    <n v="1260"/>
+    <n v="2307"/>
+  </r>
+  <r>
+    <s v="000261753"/>
+    <x v="17"/>
+    <n v="18"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="39"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="3"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="3129"/>
+    <n v="3756"/>
+    <n v="6885"/>
+  </r>
+  <r>
+    <s v="000261754"/>
+    <x v="17"/>
+    <n v="18"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="26"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261755"/>
+    <x v="17"/>
+    <n v="18"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="36"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261756"/>
+    <x v="18"/>
+    <n v="19"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="17"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="13"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="14"/>
+    <n v="4"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="4216"/>
+    <n v="5064"/>
+    <n v="9280"/>
+  </r>
+  <r>
+    <s v="000261757"/>
+    <x v="18"/>
+    <n v="19"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="19"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="15"/>
+    <n v="4"/>
+    <n v="295"/>
+    <n v="540"/>
+    <n v="980"/>
+    <n v="1180"/>
+    <n v="2160"/>
+  </r>
+  <r>
+    <s v="000261758"/>
+    <x v="18"/>
+    <n v="19"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="25"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="4"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="4172"/>
+    <n v="5008"/>
+    <n v="9180"/>
+  </r>
+  <r>
+    <s v="000261759"/>
+    <x v="18"/>
+    <n v="19"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="35"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="16"/>
+    <n v="4"/>
+    <n v="1898"/>
+    <n v="3375"/>
+    <n v="5908"/>
+    <n v="7592"/>
+    <n v="13500"/>
+  </r>
+  <r>
+    <s v="000261760"/>
+    <x v="18"/>
+    <n v="19"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="37"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="4"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="4172"/>
+    <n v="5008"/>
+    <n v="9180"/>
+  </r>
+  <r>
+    <s v="000261761"/>
+    <x v="18"/>
+    <n v="19"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="39"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="4172"/>
+    <n v="5008"/>
+    <n v="9180"/>
+  </r>
+  <r>
+    <s v="000261762"/>
+    <x v="18"/>
+    <n v="19"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="63"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="4172"/>
+    <n v="5008"/>
+    <n v="9180"/>
+  </r>
+  <r>
+    <s v="000261763"/>
+    <x v="18"/>
+    <n v="19"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="18"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="11"/>
+    <n v="2"/>
+    <n v="295"/>
+    <n v="540"/>
+    <n v="490"/>
+    <n v="590"/>
+    <n v="1080"/>
+  </r>
+  <r>
+    <s v="000261764"/>
+    <x v="18"/>
+    <n v="19"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="56"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="15"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="2086"/>
+    <n v="2504"/>
+    <n v="4590"/>
+  </r>
+  <r>
+    <s v="000261765"/>
+    <x v="18"/>
+    <n v="19"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="39"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="11"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="13926"/>
+    <n v="25520"/>
+  </r>
+  <r>
+    <s v="000261766"/>
+    <x v="19"/>
+    <n v="20"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="33"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="10"/>
+    <n v="4"/>
+    <n v="1898"/>
+    <n v="3375"/>
+    <n v="5908"/>
+    <n v="7592"/>
+    <n v="13500"/>
+  </r>
+  <r>
+    <s v="000261767"/>
+    <x v="19"/>
+    <n v="20"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="57"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="4172"/>
+    <n v="5008"/>
+    <n v="9180"/>
+  </r>
+  <r>
+    <s v="000261768"/>
+    <x v="19"/>
+    <n v="20"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="29"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="17"/>
+    <n v="3"/>
+    <n v="295"/>
+    <n v="540"/>
+    <n v="735"/>
+    <n v="885"/>
+    <n v="1620"/>
+  </r>
+  <r>
+    <s v="000261769"/>
+    <x v="19"/>
+    <n v="20"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="35"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261770"/>
+    <x v="19"/>
+    <n v="20"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="35"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261771"/>
+    <x v="20"/>
+    <n v="21"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="26"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="16"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="3"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="3162"/>
+    <n v="3798"/>
+    <n v="6960"/>
+  </r>
+  <r>
+    <s v="000261772"/>
+    <x v="20"/>
+    <n v="21"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="23"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="2"/>
+    <n v="420"/>
+    <n v="769"/>
+    <n v="698"/>
+    <n v="840"/>
+    <n v="1538"/>
+  </r>
+  <r>
+    <s v="000261773"/>
+    <x v="21"/>
+    <n v="22"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="30"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="3"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="3162"/>
+    <n v="3798"/>
+    <n v="6960"/>
+  </r>
+  <r>
+    <s v="000261774"/>
+    <x v="21"/>
+    <n v="22"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="41"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="3"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="3129"/>
+    <n v="3756"/>
+    <n v="6885"/>
+  </r>
+  <r>
+    <s v="000261775"/>
+    <x v="21"/>
+    <n v="22"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="19"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="8"/>
+    <n v="1"/>
+    <n v="308"/>
+    <n v="565"/>
+    <n v="257"/>
+    <n v="308"/>
+    <n v="565"/>
+  </r>
+  <r>
+    <s v="000261776"/>
+    <x v="21"/>
+    <n v="22"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="25"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261777"/>
+    <x v="21"/>
+    <n v="22"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="27"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261778"/>
+    <x v="21"/>
+    <n v="22"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="41"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="15"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261779"/>
+    <x v="22"/>
+    <n v="23"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="30"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="1266"/>
+    <n v="2320"/>
+    <n v="1054"/>
+    <n v="1266"/>
+    <n v="2320"/>
+  </r>
+  <r>
+    <s v="000261780"/>
+    <x v="22"/>
+    <n v="23"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="31"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="1"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="1043"/>
+    <n v="1252"/>
+    <n v="2295"/>
+  </r>
+  <r>
+    <s v="000261781"/>
+    <x v="22"/>
+    <n v="23"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="35"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="9"/>
+    <n v="1"/>
+    <n v="295"/>
+    <n v="540"/>
+    <n v="245"/>
+    <n v="295"/>
+    <n v="540"/>
+  </r>
+  <r>
+    <s v="000261782"/>
+    <x v="23"/>
+    <n v="24"/>
+    <x v="0"/>
+    <n v="2021"/>
+    <n v="38"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="4"/>
+    <n v="1252"/>
+    <n v="2295"/>
+    <n v="4172"/>
+    <n v="5008"/>
+    <n v="9180"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA0D3F03-89D5-4DD7-9D52-CAEAF3C22DEA}" name="TablaDinámica1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A1:B26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="14" showAll="0" sortType="descending">
+      <items count="25">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="18">
+        <item x="6"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="16"/>
+        <item x="14"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="19">
+        <item x="10"/>
+        <item x="16"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="15"/>
+        <item x="17"/>
+        <item x="13"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="25">
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de Order_Quantity" fld="13" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1121,7 +5439,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1227,7 +5545,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1369,33 +5687,463 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE6C59B9-C105-46B7-941B-273388CBCCE3}">
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7265625" customWidth="1"/>
+    <col min="8" max="8" width="19.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="10">
+        <v>44549</v>
+      </c>
+      <c r="B2" s="11">
+        <v>43</v>
+      </c>
+      <c r="D2" s="10">
+        <v>44531</v>
+      </c>
+      <c r="E2" s="11">
+        <v>5</v>
+      </c>
+      <c r="G2" s="13">
+        <f>LARGE($E$2:$E$25,1)</f>
+        <v>43</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="10">
+        <v>44548</v>
+      </c>
+      <c r="B3" s="11">
+        <v>19</v>
+      </c>
+      <c r="D3" s="10">
+        <v>44532</v>
+      </c>
+      <c r="E3" s="11">
+        <v>3</v>
+      </c>
+      <c r="G3" s="13"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="10">
+        <v>44550</v>
+      </c>
+      <c r="B4" s="11">
+        <v>13</v>
+      </c>
+      <c r="D4" s="10">
+        <v>44533</v>
+      </c>
+      <c r="E4" s="11">
+        <v>4</v>
+      </c>
+      <c r="G4" s="13" cm="1">
+        <f t="array" ref="G4:G8">LARGE($E$2:$E$25,ROW($1:$5))</f>
+        <v>43</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="10">
+        <v>44542</v>
+      </c>
+      <c r="B5" s="11">
+        <v>12</v>
+      </c>
+      <c r="D5" s="10">
+        <v>44534</v>
+      </c>
+      <c r="E5" s="11">
+        <v>4</v>
+      </c>
+      <c r="G5" s="13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="10">
+        <v>44538</v>
+      </c>
+      <c r="B6" s="11">
+        <v>11</v>
+      </c>
+      <c r="D6" s="10">
+        <v>44535</v>
+      </c>
+      <c r="E6" s="11">
+        <v>10</v>
+      </c>
+      <c r="G6" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="10">
+        <v>44535</v>
+      </c>
+      <c r="B7" s="11">
+        <v>10</v>
+      </c>
+      <c r="D7" s="10">
+        <v>44536</v>
+      </c>
+      <c r="E7" s="11">
+        <v>6</v>
+      </c>
+      <c r="G7" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="10">
+        <v>44552</v>
+      </c>
+      <c r="B8" s="11">
+        <v>10</v>
+      </c>
+      <c r="D8" s="10">
+        <v>44537</v>
+      </c>
+      <c r="E8" s="11">
+        <v>6</v>
+      </c>
+      <c r="G8" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="10">
+        <v>44541</v>
+      </c>
+      <c r="B9" s="11">
+        <v>8</v>
+      </c>
+      <c r="D9" s="10">
+        <v>44538</v>
+      </c>
+      <c r="E9" s="11">
+        <v>11</v>
+      </c>
+      <c r="G9" s="13"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="10">
+        <v>44540</v>
+      </c>
+      <c r="B10" s="11">
+        <v>8</v>
+      </c>
+      <c r="D10" s="10">
+        <v>44539</v>
+      </c>
+      <c r="E10" s="11">
+        <v>3</v>
+      </c>
+      <c r="G10" s="13" cm="1">
+        <f t="array" ref="G10:G15">SMALL($E$2:$E$25,ROW($1:$6))</f>
+        <v>1</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="10">
+        <v>44537</v>
+      </c>
+      <c r="B11" s="11">
+        <v>6</v>
+      </c>
+      <c r="D11" s="10">
+        <v>44540</v>
+      </c>
+      <c r="E11" s="11">
+        <v>8</v>
+      </c>
+      <c r="G11" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="10">
+        <v>44536</v>
+      </c>
+      <c r="B12" s="11">
+        <v>6</v>
+      </c>
+      <c r="D12" s="10">
+        <v>44541</v>
+      </c>
+      <c r="E12" s="11">
+        <v>8</v>
+      </c>
+      <c r="G12" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="10">
+        <v>44543</v>
+      </c>
+      <c r="B13" s="11">
+        <v>6</v>
+      </c>
+      <c r="D13" s="10">
+        <v>44542</v>
+      </c>
+      <c r="E13" s="11">
+        <v>12</v>
+      </c>
+      <c r="G13" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="10">
+        <v>44551</v>
+      </c>
+      <c r="B14" s="11">
+        <v>5</v>
+      </c>
+      <c r="D14" s="10">
+        <v>44543</v>
+      </c>
+      <c r="E14" s="11">
+        <v>6</v>
+      </c>
+      <c r="G14" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="10">
+        <v>44531</v>
+      </c>
+      <c r="B15" s="11">
+        <v>5</v>
+      </c>
+      <c r="D15" s="10">
+        <v>44544</v>
+      </c>
+      <c r="E15" s="11">
+        <v>4</v>
+      </c>
+      <c r="G15" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="10">
+        <v>44546</v>
+      </c>
+      <c r="B16" s="11">
+        <v>5</v>
+      </c>
+      <c r="D16" s="10">
+        <v>44545</v>
+      </c>
+      <c r="E16" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="10">
+        <v>44534</v>
+      </c>
+      <c r="B17" s="11">
+        <v>4</v>
+      </c>
+      <c r="D17" s="10">
+        <v>44546</v>
+      </c>
+      <c r="E17" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="10">
+        <v>44554</v>
+      </c>
+      <c r="B18" s="11">
+        <v>4</v>
+      </c>
+      <c r="D18" s="10">
+        <v>44547</v>
+      </c>
+      <c r="E18" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="10">
+        <v>44547</v>
+      </c>
+      <c r="B19" s="11">
+        <v>4</v>
+      </c>
+      <c r="D19" s="10">
+        <v>44548</v>
+      </c>
+      <c r="E19" s="11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="10">
+        <v>44533</v>
+      </c>
+      <c r="B20" s="11">
+        <v>4</v>
+      </c>
+      <c r="D20" s="10">
+        <v>44549</v>
+      </c>
+      <c r="E20" s="11">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="10">
+        <v>44544</v>
+      </c>
+      <c r="B21" s="11">
+        <v>4</v>
+      </c>
+      <c r="D21" s="10">
+        <v>44550</v>
+      </c>
+      <c r="E21" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="10">
+        <v>44532</v>
+      </c>
+      <c r="B22" s="11">
+        <v>3</v>
+      </c>
+      <c r="D22" s="10">
+        <v>44551</v>
+      </c>
+      <c r="E22" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="10">
+        <v>44553</v>
+      </c>
+      <c r="B23" s="11">
+        <v>3</v>
+      </c>
+      <c r="D23" s="10">
+        <v>44552</v>
+      </c>
+      <c r="E23" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
+        <v>44539</v>
+      </c>
+      <c r="B24" s="11">
+        <v>3</v>
+      </c>
+      <c r="D24" s="10">
+        <v>44553</v>
+      </c>
+      <c r="E24" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>44545</v>
+      </c>
+      <c r="B25" s="11">
+        <v>1</v>
+      </c>
+      <c r="D25" s="10">
+        <v>44554</v>
+      </c>
+      <c r="E25" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B26" s="11">
+        <v>197</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:E25">
+    <sortCondition ref="D2:D25"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:S89"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1454,7 +6202,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>19</v>
       </c>
@@ -1515,7 +6263,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
@@ -1576,7 +6324,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
@@ -1637,7 +6385,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
@@ -1698,7 +6446,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
@@ -1759,7 +6507,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
@@ -1820,7 +6568,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
@@ -1881,7 +6629,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>46</v>
       </c>
@@ -1942,7 +6690,7 @@
         <v>3076</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>47</v>
       </c>
@@ -2003,7 +6751,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>48</v>
       </c>
@@ -2064,7 +6812,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>51</v>
       </c>
@@ -2125,7 +6873,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>54</v>
       </c>
@@ -2186,7 +6934,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>55</v>
       </c>
@@ -2247,7 +6995,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>56</v>
       </c>
@@ -2308,7 +7056,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>59</v>
       </c>
@@ -2369,7 +7117,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>61</v>
       </c>
@@ -2430,7 +7178,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>62</v>
       </c>
@@ -2491,7 +7239,7 @@
         <v>3076</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>64</v>
       </c>
@@ -2552,7 +7300,7 @@
         <v>4640</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>65</v>
       </c>
@@ -2613,7 +7361,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -2674,7 +7422,7 @@
         <v>9280</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>68</v>
       </c>
@@ -2735,7 +7483,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>71</v>
       </c>
@@ -2796,7 +7544,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>72</v>
       </c>
@@ -2857,7 +7605,7 @@
         <v>6750</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>75</v>
       </c>
@@ -2918,7 +7666,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>77</v>
       </c>
@@ -2979,7 +7727,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>78</v>
       </c>
@@ -3040,7 +7788,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>79</v>
       </c>
@@ -3101,7 +7849,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>80</v>
       </c>
@@ -3162,7 +7910,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>82</v>
       </c>
@@ -3223,7 +7971,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>84</v>
       </c>
@@ -3284,7 +8032,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>85</v>
       </c>
@@ -3345,7 +8093,7 @@
         <v>6885</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>88</v>
       </c>
@@ -3406,7 +8154,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>89</v>
       </c>
@@ -3467,7 +8215,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>90</v>
       </c>
@@ -3528,7 +8276,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>91</v>
       </c>
@@ -3589,7 +8337,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>92</v>
       </c>
@@ -3650,7 +8398,7 @@
         <v>9280</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>93</v>
       </c>
@@ -3711,7 +8459,7 @@
         <v>3076</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>94</v>
       </c>
@@ -3772,7 +8520,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>95</v>
       </c>
@@ -3833,7 +8581,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>96</v>
       </c>
@@ -3894,7 +8642,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>97</v>
       </c>
@@ -3955,7 +8703,7 @@
         <v>6960</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>98</v>
       </c>
@@ -4016,7 +8764,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>100</v>
       </c>
@@ -4077,7 +8825,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>101</v>
       </c>
@@ -4138,7 +8886,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>102</v>
       </c>
@@ -4199,7 +8947,7 @@
         <v>4640</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>103</v>
       </c>
@@ -4260,7 +9008,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>104</v>
       </c>
@@ -4321,7 +9069,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>105</v>
       </c>
@@ -4382,7 +9130,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>106</v>
       </c>
@@ -4443,7 +9191,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>107</v>
       </c>
@@ -4504,7 +9252,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>108</v>
       </c>
@@ -4565,7 +9313,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>111</v>
       </c>
@@ -4626,7 +9374,7 @@
         <v>4640</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>112</v>
       </c>
@@ -4687,7 +9435,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>113</v>
       </c>
@@ -4748,7 +9496,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>114</v>
       </c>
@@ -4809,7 +9557,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>115</v>
       </c>
@@ -4870,7 +9618,7 @@
         <v>9280</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>116</v>
       </c>
@@ -4931,7 +9679,7 @@
         <v>6960</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>118</v>
       </c>
@@ -4992,7 +9740,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>119</v>
       </c>
@@ -5053,7 +9801,7 @@
         <v>6885</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>120</v>
       </c>
@@ -5114,7 +9862,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>121</v>
       </c>
@@ -5175,7 +9923,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>122</v>
       </c>
@@ -5236,7 +9984,7 @@
         <v>9280</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>124</v>
       </c>
@@ -5297,7 +10045,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>126</v>
       </c>
@@ -5358,7 +10106,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>127</v>
       </c>
@@ -5419,7 +10167,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>129</v>
       </c>
@@ -5480,7 +10228,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>130</v>
       </c>
@@ -5541,7 +10289,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>131</v>
       </c>
@@ -5602,7 +10350,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>132</v>
       </c>
@@ -5663,7 +10411,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>134</v>
       </c>
@@ -5724,7 +10472,7 @@
         <v>4590</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>136</v>
       </c>
@@ -5785,7 +10533,7 @@
         <v>25520</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>137</v>
       </c>
@@ -5846,7 +10594,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>138</v>
       </c>
@@ -5907,7 +10655,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>139</v>
       </c>
@@ -5968,7 +10716,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>141</v>
       </c>
@@ -6029,7 +10777,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>142</v>
       </c>
@@ -6090,7 +10838,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>143</v>
       </c>
@@ -6151,7 +10899,7 @@
         <v>6960</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>145</v>
       </c>
@@ -6212,7 +10960,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>146</v>
       </c>
@@ -6273,7 +11021,7 @@
         <v>6960</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>147</v>
       </c>
@@ -6334,7 +11082,7 @@
         <v>6885</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>148</v>
       </c>
@@ -6395,7 +11143,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>149</v>
       </c>
@@ -6456,7 +11204,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>150</v>
       </c>
@@ -6517,7 +11265,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>151</v>
       </c>
@@ -6578,7 +11326,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>152</v>
       </c>
@@ -6639,7 +11387,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>153</v>
       </c>
@@ -6700,7 +11448,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>154</v>
       </c>
@@ -6761,7 +11509,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>155</v>
       </c>
@@ -6823,8 +11571,16 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:S89" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <dateGroupItem year="2021" month="12" day="19" dateTimeGrouping="day"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7066,15 +11822,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="6cf0ffbd-cd96-4ba4-bd4f-bd34e8409846">
@@ -7093,14 +11840,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A449075-01A6-451D-9F66-A0FA0F4FD7AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A449075-01A6-451D-9F66-A0FA0F4FD7AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6cf0ffbd-cd96-4ba4-bd4f-bd34e8409846"/>
+    <ds:schemaRef ds:uri="ef7ae401-bd17-41a5-97cb-ef653218410e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38B93B57-25C3-448B-BDF9-E62880BE52EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07A2BFF5-7901-4AE1-9EAC-C53400A8AC57}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6cf0ffbd-cd96-4ba4-bd4f-bd34e8409846"/>
+    <ds:schemaRef ds:uri="ef7ae401-bd17-41a5-97cb-ef653218410e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07A2BFF5-7901-4AE1-9EAC-C53400A8AC57}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38B93B57-25C3-448B-BDF9-E62880BE52EE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Bike_Sales_Outlier_Lab.xlsx
+++ b/Bike_Sales_Outlier_Lab.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01D0575-94E9-4BB2-8F43-A174AB047243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78FB299-346F-40AC-B732-EBA1559723A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="3" r:id="rId1"/>
@@ -3114,16 +3114,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>439964</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>2722</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>449036</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>175079</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>263071</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>81643</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>272143</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>72572</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
